--- a/rover_platform_mbse/system/ARDENNES-ROVER_ROS_SYS-SR-V-002.xlsx
+++ b/rover_platform_mbse/system/ARDENNES-ROVER_ROS_SYS-SR-V-002.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="491" uniqueCount="302">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="494" uniqueCount="305">
   <si>
     <t xml:space="preserve">No</t>
   </si>
@@ -143,13 +143,13 @@
     <t xml:space="preserve">Performance</t>
   </si>
   <si>
-    <t xml:space="preserve">The rover platform shall limit linear velocity to a maximum of 1.0 m/s and angular velocity to a maximum of 1.7 rad/s, for commands from any source.</t>
+    <t xml:space="preserve">The rover platform shall limit linear velocity to a maximum of 1.2 m/s and angular velocity to a maximum of 1.7 rad/s, for commands from any source.</t>
   </si>
   <si>
     <t xml:space="preserve">Safety speed limit for operation around people.</t>
   </si>
   <si>
-    <t xml:space="preserve">Commands above the limit result in a measured speed &lt;= 1.05 m/s (and &lt;= angular limit) on flat hard ground.</t>
+    <t xml:space="preserve">Commands above the limit result in a measured speed &lt;= 1.26 m/s (and &lt;= angular limit) on flat hard ground.</t>
   </si>
   <si>
     <t xml:space="preserve">SYS-SR-005, SYS-SR-013</t>
@@ -930,6 +930,15 @@
   </si>
   <si>
     <t xml:space="preserve">Added the Mass Properties sheet (SolidWorks ROVER_1000_WATT_VARIANT), CAD evidence for SYS-SR-001, and the related open questions.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-10-27</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Radu Potlog (prepared with Claude Code)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SYS-SR-004: linear velocity limit raised from 1.0 to 1.2 m/s (acceptance 1.05 -&gt; 1.26 m/s) after the DCC1020 on-board speed loop replaced the DCC1000 and host wheel PIDs; angular limit unchanged at 1.7 rad/s. Status stays Draft.</t>
   </si>
 </sst>
 </file>
@@ -2913,7 +2922,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:D4"/>
+  <dimension ref="A1:D5"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="10.21"/>
@@ -2978,6 +2987,20 @@
         <v>301</v>
       </c>
     </row>
+    <row r="5" customFormat="false" ht="38.0" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="4" t="s">
+        <v>297</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>302</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>303</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>304</v>
+      </c>
+    </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7875" right="0.7875" top="1.025" bottom="1.025" header="0.7875" footer="0.7875"/>
